--- a/Logger/Korrelationstabelle_MTM.xlsx
+++ b/Logger/Korrelationstabelle_MTM.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alexandra\Documents\GitHub\Moore-Lichtenau-Meusebach\Logger\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6E027A0-4357-4D72-A348-D14480AD3E19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7BF36C7-A686-4CAE-A52C-02982132A8F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$D$101</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$D$1</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="14">
   <si>
     <t>MTM_var</t>
   </si>
@@ -34,13 +34,10 @@
     <t>Other_Logger</t>
   </si>
   <si>
-    <t>correlation</t>
-  </si>
-  <si>
     <t>Temp_sonne_C</t>
   </si>
   <si>
-    <t>MTO</t>
+    <t>MTM</t>
   </si>
   <si>
     <t>Temp_schatten_C</t>
@@ -55,6 +52,9 @@
     <t>Licht_lux</t>
   </si>
   <si>
+    <t>MTO</t>
+  </si>
+  <si>
     <t>MTW</t>
   </si>
   <si>
@@ -62,6 +62,9 @@
   </si>
   <si>
     <t>MTS</t>
+  </si>
+  <si>
+    <t>Korrelation</t>
   </si>
 </sst>
 </file>
@@ -120,13 +123,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -433,13 +442,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:D101"/>
+  <dimension ref="A1:D126"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="19.85546875" customWidth="1"/>
-    <col min="3" max="3" width="13.7109375" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" customWidth="1"/>
+    <col min="1" max="2" width="18.5703125" customWidth="1"/>
+    <col min="3" max="3" width="15" customWidth="1"/>
+    <col min="4" max="4" width="12.5703125" style="5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -453,1420 +461,1761 @@
         <v>2</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" s="2">
-        <v>0.95570302255305095</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+      <c r="D2" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" s="2">
-        <v>0.91395857823771021</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.90013242646659808</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" s="2">
-        <v>-0.80117095480930611</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+      <c r="D4" s="4">
+        <v>-0.807719890961757</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D5" s="2">
-        <v>0.4703309630079941</v>
+        <v>4</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.43496818333414011</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D6" s="2">
-        <v>0.82268063781526812</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+      <c r="D6" s="4">
+        <v>0.8152639161629639</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D7" s="2">
-        <v>0.90759659946555304</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+      <c r="D7" s="4">
+        <v>0.90013242646659808</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D8" s="2">
-        <v>0.98641658426274448</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+      <c r="D8" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D9" s="2">
-        <v>-0.77139846350686347</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+      <c r="D9" s="4">
+        <v>-0.79108309110340669</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D10" s="2">
-        <v>0.64018527485593002</v>
+        <v>4</v>
+      </c>
+      <c r="D10" s="4">
+        <v>0.63640758602022751</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D11" s="2">
-        <v>0.76257625978730981</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+      <c r="D11" s="4">
+        <v>0.56594453074999673</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D12" s="2">
-        <v>0.90387534963583283</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+      <c r="D12" s="4">
+        <v>-0.807719890961757</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D13" s="2">
-        <v>-0.78340813252216523</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+      <c r="D13" s="4">
+        <v>-0.79108309110340669</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D14" s="2">
-        <v>0.98272017563887848</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+      <c r="D14" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D15" s="2">
-        <v>-6.2167866720999367E-2</v>
+        <v>4</v>
+      </c>
+      <c r="D15" s="4">
+        <v>-4.9195099444528489E-2</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D16" s="2">
-        <v>0.69721113188808603</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+      <c r="D16" s="4">
+        <v>-0.6181901436689502</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D17" s="2">
-        <v>0.89457967723371534</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+      <c r="D17" s="4">
+        <v>0.43496818333414011</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D18" s="2">
-        <v>0.58325240934456224</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+      <c r="D18" s="4">
+        <v>0.63640758602022751</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D19" s="2">
-        <v>3.8625316339334068E-3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+      <c r="D19" s="4">
+        <v>-4.9195099444528489E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D20" s="2">
-        <v>0.97566370639655098</v>
+        <v>4</v>
+      </c>
+      <c r="D20" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D21" s="2">
-        <v>0.68907593118401889</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+      <c r="D21" s="4">
+        <v>0.1205513538615286</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D22" s="2">
-        <v>0.88478866845068904</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+      <c r="D22" s="4">
+        <v>0.8152639161629639</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D23" s="2">
-        <v>0.57623574194182892</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+      <c r="D23" s="4">
+        <v>0.56594453074999673</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D24" s="2">
-        <v>-0.60700932466956936</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+      <c r="D24" s="4">
+        <v>-0.6181901436689502</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D25" s="2">
-        <v>0.15250169614842651</v>
+        <v>4</v>
+      </c>
+      <c r="D25" s="4">
+        <v>0.1205513538615286</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D26" s="2">
-        <v>0.67408690543250938</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+      <c r="D26" s="4">
+        <v>0.99999999999999978</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D27" s="2">
-        <v>0.8459676441589169</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+      <c r="D27" s="4">
+        <v>0.90387534963583283</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D28" s="2">
-        <v>0.82373791372955951</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+      <c r="D28" s="4">
+        <v>0.91395857823771021</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D29" s="2">
-        <v>-0.70787705055813721</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+      <c r="D29" s="4">
+        <v>-0.80117095480930611</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D30" s="2">
-        <v>0.46275855626541418</v>
+        <v>9</v>
+      </c>
+      <c r="D30" s="4">
+        <v>0.4703309630079941</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D31" s="2">
-        <v>0.63771350176580899</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+      <c r="D31" s="4">
+        <v>0.63644788599726454</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D32" s="2">
+        <v>9</v>
+      </c>
+      <c r="D32" s="4">
         <v>0.84072727915346579</v>
       </c>
     </row>
-    <row r="33" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D33" s="2">
-        <v>0.85959541399075923</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+      <c r="D33" s="4">
+        <v>0.98641658426274448</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D34" s="2">
-        <v>-0.63183122360981203</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+      <c r="D34" s="4">
+        <v>-0.77139846350686347</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D35" s="2">
-        <v>0.72403408078447773</v>
+        <v>9</v>
+      </c>
+      <c r="D35" s="4">
+        <v>0.64018527485593002</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D36" s="2">
-        <v>0.63644788599726454</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+      <c r="D36" s="4">
+        <v>0.48599620399760468</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D37" s="2">
-        <v>0.80369910334616002</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+      <c r="D37" s="4">
+        <v>-0.76870472872206386</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D38" s="2">
-        <v>-0.6305557582858502</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+      <c r="D38" s="4">
+        <v>-0.78340813252216523</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D39" s="2">
-        <v>0.77536888467174403</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+      <c r="D39" s="4">
+        <v>0.98272017563887848</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D40" s="2">
-        <v>-0.199857142674811</v>
+        <v>9</v>
+      </c>
+      <c r="D40" s="4">
+        <v>-6.2167866720999367E-2</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D41" s="2">
-        <v>0.63635854003269621</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+      <c r="D41" s="4">
+        <v>-0.56526137107275565</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D42" s="2">
-        <v>0.78683362544686941</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+      <c r="D42" s="4">
+        <v>0.35762431378813769</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D43" s="2">
-        <v>0.65335964168237304</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+      <c r="D43" s="4">
+        <v>0.58325240934456224</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D44" s="2">
-        <v>-0.15386457879305529</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+      <c r="D44" s="4">
+        <v>3.8625316339334068E-3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D45" s="2">
-        <v>0.9136870109516867</v>
+        <v>9</v>
+      </c>
+      <c r="D45" s="4">
+        <v>0.97566370639655098</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D46" s="2">
-        <v>0.56404813637263529</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+      <c r="D46" s="4">
+        <v>4.3551084891451229E-2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D47" s="2">
+        <v>9</v>
+      </c>
+      <c r="D47" s="4">
         <v>0.73471208197911286</v>
       </c>
     </row>
-    <row r="48" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D48" s="2">
-        <v>0.43761869077876753</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+      <c r="D48" s="4">
+        <v>0.57623574194182892</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D49" s="2">
-        <v>-0.45382477530962312</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+      <c r="D49" s="4">
+        <v>-0.60700932466956936</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D50" s="2">
-        <v>0.14914080085092299</v>
+        <v>9</v>
+      </c>
+      <c r="D50" s="4">
+        <v>0.15250169614842651</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D51" s="2">
-        <v>0.51641786891722319</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+      <c r="D51" s="4">
+        <v>0.69721113188808603</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D52" s="2">
-        <v>0.64575517635531299</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D52" s="4">
+        <v>0.88478866845068904</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D53" s="2">
-        <v>0.87434839673961318</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="D53" s="4">
+        <v>0.82373791372955951</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D54" s="2">
-        <v>-0.77616785184864001</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="D54" s="4">
+        <v>-0.70787705055813721</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D55" s="2">
-        <v>0.43922105624581198</v>
+        <v>10</v>
+      </c>
+      <c r="D55" s="4">
+        <v>0.46275855626541418</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D56" s="2">
-        <v>0.49423181455165471</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="D56" s="4">
+        <v>0.68907593118401889</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D57" s="2">
-        <v>0.60251232837022217</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="D57" s="4">
+        <v>0.80369910334616002</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D58" s="2">
-        <v>0.99270178843834178</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="D58" s="4">
+        <v>0.85959541399075923</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D59" s="2">
-        <v>-0.78829325318893262</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="D59" s="4">
+        <v>-0.63183122360981203</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D60" s="2">
-        <v>0.62778383609341037</v>
+        <v>10</v>
+      </c>
+      <c r="D60" s="4">
+        <v>0.72403408078447773</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D61" s="2">
-        <v>0.48599620399760468</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="D61" s="4">
+        <v>0.51641786891722319</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D62" s="2">
-        <v>0.48852111649936769</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="D62" s="4">
+        <v>-0.71374883016685164</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D63" s="2">
-        <v>-0.77144419023946065</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="D63" s="4">
+        <v>-0.6305557582858502</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D64" s="2">
-        <v>0.98248567227391159</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="D64" s="4">
+        <v>0.77536888467174403</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D65" s="2">
-        <v>-4.2359046819525688E-2</v>
+        <v>10</v>
+      </c>
+      <c r="D65" s="4">
+        <v>-0.199857142674811</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D66" s="2">
-        <v>0.16646496057656529</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="D66" s="4">
+        <v>-0.58564535026855558</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D67" s="2">
+      <c r="D67" s="4">
         <v>0.46251860530097222</v>
       </c>
     </row>
-    <row r="68" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D68" s="2">
-        <v>0.6804016337770058</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="D68" s="4">
+        <v>0.65335964168237304</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D69" s="2">
-        <v>-0.11542822820072721</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="D69" s="4">
+        <v>-0.15386457879305529</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D70" s="2">
-        <v>0.97982758387623636</v>
+        <v>10</v>
+      </c>
+      <c r="D70" s="4">
+        <v>0.9136870109516867</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D71" s="2">
+      <c r="D71" s="4">
         <v>0.1462666456689265</v>
       </c>
     </row>
-    <row r="72" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D72" s="2">
-        <v>0.35762431378813769</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="D72" s="4">
+        <v>0.64575517635531299</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D73" s="2">
-        <v>0.57311779313517763</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="D73" s="4">
+        <v>0.43761869077876753</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D74" s="2">
-        <v>-0.59844748749700127</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="D74" s="4">
+        <v>-0.45382477530962312</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D75" s="2">
-        <v>0.1625429875264108</v>
+        <v>10</v>
+      </c>
+      <c r="D75" s="4">
+        <v>0.14914080085092299</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D76" s="2">
-        <v>4.3551084891451229E-2</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="D76" s="4">
+        <v>0.67408690543250938</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D77" s="2">
-        <v>0.3290117430710201</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="D77" s="4">
+        <v>0.95570302255305095</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D78" s="2">
-        <v>0.93334174014954552</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="D78" s="4">
+        <v>0.87434839673961318</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D79" s="2">
-        <v>-0.76489240669286696</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="D79" s="4">
+        <v>-0.77616785184864001</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D80" s="2">
-        <v>0.5719395455827847</v>
+        <v>11</v>
+      </c>
+      <c r="D80" s="4">
+        <v>0.43922105624581198</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D81" s="2">
-        <v>1.6820872551199791E-2</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="D81" s="4">
+        <v>0.76257625978730981</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D82" s="2">
-        <v>-0.71374883016685164</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="D82" s="4">
+        <v>0.89457967723371534</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D83" s="2">
-        <v>0.98951809344835107</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="D83" s="4">
+        <v>0.99270178843834178</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D84" s="2">
-        <v>-0.75967468702902707</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="D84" s="4">
+        <v>-0.78829325318893262</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D85" s="2">
-        <v>0.66531036468565297</v>
+        <v>11</v>
+      </c>
+      <c r="D85" s="4">
+        <v>0.62778383609341037</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D86" s="2">
-        <v>-0.56526137107275565</v>
-      </c>
-    </row>
-    <row r="87" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="D86" s="4">
+        <v>0.56404813637263529</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D87" s="2">
-        <v>-0.76870472872206386</v>
-      </c>
-    </row>
-    <row r="88" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="D87" s="4">
+        <v>-0.78371468880580952</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D88" s="2">
-        <v>-0.77031074030932545</v>
-      </c>
-    </row>
-    <row r="89" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="D88" s="4">
+        <v>-0.77144419023946065</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D89" s="2">
-        <v>0.98675748669042562</v>
-      </c>
-    </row>
-    <row r="90" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="D89" s="4">
+        <v>0.98248567227391159</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D90" s="2">
-        <v>-3.4281098953398398E-2</v>
+        <v>11</v>
+      </c>
+      <c r="D90" s="4">
+        <v>-4.2359046819525688E-2</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D91" s="2">
-        <v>-0.58564535026855558</v>
-      </c>
-    </row>
-    <row r="92" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="D91" s="4">
+        <v>-0.59885733516535478</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D92" s="2">
-        <v>-0.77682802182905109</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="D92" s="4">
+        <v>0.48852111649936769</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D93" s="2">
-        <v>0.56289946570777971</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="D93" s="4">
+        <v>0.6804016337770058</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D94" s="2">
-        <v>2.6172249503399941E-2</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="D94" s="4">
+        <v>-0.11542822820072721</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D95" s="2">
-        <v>0.97676030221017829</v>
+        <v>11</v>
+      </c>
+      <c r="D95" s="4">
+        <v>0.97982758387623636</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B96" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D96" s="2">
-        <v>-0.59192944260877245</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="D96" s="4">
+        <v>0.16646496057656529</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D97" s="2">
-        <v>-0.78371468880580952</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D97" s="4">
+        <v>0.78683362544686941</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D98" s="2">
-        <v>0.440462298722682</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="D98" s="4">
+        <v>0.57311779313517763</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D99" s="2">
-        <v>-0.44928446834063052</v>
-      </c>
-    </row>
-    <row r="100" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="D99" s="4">
+        <v>-0.59844748749700127</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D100" s="2">
-        <v>0.1698796420073084</v>
+        <v>11</v>
+      </c>
+      <c r="D100" s="4">
+        <v>0.1625429875264108</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D101" s="2">
-        <v>-0.59885733516535478</v>
+      <c r="D101" s="4">
+        <v>0.82268063781526812</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A102" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D102" s="4">
+        <v>0.90759659946555304</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A103" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D103" s="4">
+        <v>0.93334174014954552</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A104" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D104" s="4">
+        <v>-0.76489240669286696</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A105" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D105" s="4">
+        <v>0.5719395455827847</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A106" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D106" s="4">
+        <v>0.63771350176580899</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A107" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D107" s="4">
+        <v>0.8459676441589169</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A108" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D108" s="4">
+        <v>0.98951809344835107</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A109" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B109" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D109" s="4">
+        <v>-0.75967468702902707</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A110" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C110" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D110" s="4">
+        <v>0.66531036468565297</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A111" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B111" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D111" s="4">
+        <v>0.49423181455165471</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A112" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C112" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D112" s="4">
+        <v>-0.77682802182905109</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A113" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C113" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D113" s="4">
+        <v>-0.77031074030932545</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A114" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C114" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D114" s="4">
+        <v>0.98675748669042562</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A115" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B115" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C115" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D115" s="4">
+        <v>-3.4281098953398398E-2</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A116" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C116" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D116" s="4">
+        <v>-0.59192944260877245</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A117" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B117" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C117" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D117" s="4">
+        <v>0.3290117430710201</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A118" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B118" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C118" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D118" s="4">
+        <v>0.56289946570777971</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A119" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B119" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C119" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D119" s="4">
+        <v>2.6172249503399941E-2</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A120" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B120" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C120" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D120" s="4">
+        <v>0.97676030221017829</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A121" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B121" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C121" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D121" s="4">
+        <v>1.6820872551199791E-2</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A122" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B122" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C122" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D122" s="4">
+        <v>0.60251232837022217</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A123" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B123" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C123" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D123" s="4">
+        <v>0.440462298722682</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A124" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B124" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C124" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D124" s="4">
+        <v>-0.44928446834063052</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A125" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B125" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C125" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D125" s="4">
+        <v>0.1698796420073084</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A126" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C126" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D126" s="4">
+        <v>0.63635854003269621</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D101" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="Licht_lux"/>
-      </filters>
-    </filterColumn>
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A6:D101">
-      <sortCondition descending="1" ref="D1:D101"/>
-    </sortState>
-  </autoFilter>
+  <autoFilter ref="A1:D1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Logger/Korrelationstabelle_MTM.xlsx
+++ b/Logger/Korrelationstabelle_MTM.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alexandra\Documents\GitHub\Moore-Lichtenau-Meusebach\Logger\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7BF36C7-A686-4CAE-A52C-02982132A8F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DC311AF-EF61-4B28-B97F-D836B12A4A11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9525" yWindow="810" windowWidth="10290" windowHeight="9915" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$D$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$D$126</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
@@ -442,6 +442,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:D126"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -464,7 +465,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -478,7 +479,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>5</v>
       </c>
@@ -492,7 +493,7 @@
         <v>0.90013242646659808</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
@@ -506,7 +507,7 @@
         <v>-0.807719890961757</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>7</v>
       </c>
@@ -525,16 +526,16 @@
         <v>8</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>4</v>
       </c>
       <c r="D6" s="4">
-        <v>0.8152639161629639</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+        <v>0.99999999999999978</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>3</v>
       </c>
@@ -548,7 +549,7 @@
         <v>0.90013242646659808</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>5</v>
       </c>
@@ -562,7 +563,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>6</v>
       </c>
@@ -576,7 +577,7 @@
         <v>-0.79108309110340669</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>7</v>
       </c>
@@ -595,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D11" s="4">
-        <v>0.56594453074999673</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+        <v>0.82268063781526812</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>3</v>
       </c>
@@ -618,7 +619,7 @@
         <v>-0.807719890961757</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>5</v>
       </c>
@@ -632,7 +633,7 @@
         <v>-0.79108309110340669</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>6</v>
       </c>
@@ -646,7 +647,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>7</v>
       </c>
@@ -665,16 +666,16 @@
         <v>8</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>4</v>
       </c>
       <c r="D16" s="4">
-        <v>-0.6181901436689502</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+        <v>0.8152639161629639</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>3</v>
       </c>
@@ -688,7 +689,7 @@
         <v>0.43496818333414011</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>5</v>
       </c>
@@ -702,7 +703,7 @@
         <v>0.63640758602022751</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>6</v>
       </c>
@@ -716,7 +717,7 @@
         <v>-4.9195099444528489E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>7</v>
       </c>
@@ -735,16 +736,16 @@
         <v>8</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D21" s="4">
-        <v>0.1205513538615286</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+        <v>0.76257625978730981</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>3</v>
       </c>
@@ -758,7 +759,7 @@
         <v>0.8152639161629639</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>5</v>
       </c>
@@ -772,7 +773,7 @@
         <v>0.56594453074999673</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>6</v>
       </c>
@@ -786,7 +787,7 @@
         <v>-0.6181901436689502</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>7</v>
       </c>
@@ -808,13 +809,13 @@
         <v>8</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D26" s="4">
-        <v>0.99999999999999978</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+        <v>0.69721113188808603</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>3</v>
       </c>
@@ -828,7 +829,7 @@
         <v>0.90387534963583283</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>5</v>
       </c>
@@ -842,7 +843,7 @@
         <v>0.91395857823771021</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>6</v>
       </c>
@@ -856,7 +857,7 @@
         <v>-0.80117095480930611</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>7</v>
       </c>
@@ -878,13 +879,13 @@
         <v>3</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D31" s="4">
-        <v>0.63644788599726454</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+        <v>0.68907593118401889</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>3</v>
       </c>
@@ -898,7 +899,7 @@
         <v>0.84072727915346579</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>5</v>
       </c>
@@ -912,7 +913,7 @@
         <v>0.98641658426274448</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>6</v>
       </c>
@@ -926,7 +927,7 @@
         <v>-0.77139846350686347</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>7</v>
       </c>
@@ -945,16 +946,16 @@
         <v>8</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D36" s="4">
-        <v>0.48599620399760468</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+        <v>0.67408690543250938</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>3</v>
       </c>
@@ -968,7 +969,7 @@
         <v>-0.76870472872206386</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>5</v>
       </c>
@@ -982,7 +983,7 @@
         <v>-0.78340813252216523</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>6</v>
       </c>
@@ -996,7 +997,7 @@
         <v>0.98272017563887848</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>7</v>
       </c>
@@ -1015,16 +1016,16 @@
         <v>8</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D41" s="4">
-        <v>-0.56526137107275565</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+        <v>0.63771350176580899</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>3</v>
       </c>
@@ -1038,7 +1039,7 @@
         <v>0.35762431378813769</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>5</v>
       </c>
@@ -1052,7 +1053,7 @@
         <v>0.58325240934456224</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>6</v>
       </c>
@@ -1066,7 +1067,7 @@
         <v>3.8625316339334068E-3</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>7</v>
       </c>
@@ -1085,16 +1086,16 @@
         <v>8</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D46" s="4">
-        <v>4.3551084891451229E-2</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+        <v>0.63644788599726454</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>3</v>
       </c>
@@ -1108,7 +1109,7 @@
         <v>0.73471208197911286</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>5</v>
       </c>
@@ -1122,7 +1123,7 @@
         <v>0.57623574194182892</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>6</v>
       </c>
@@ -1136,7 +1137,7 @@
         <v>-0.60700932466956936</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>7</v>
       </c>
@@ -1158,13 +1159,13 @@
         <v>8</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D51" s="4">
-        <v>0.69721113188808603</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+        <v>0.63635854003269621</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>3</v>
       </c>
@@ -1178,7 +1179,7 @@
         <v>0.88478866845068904</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>5</v>
       </c>
@@ -1192,7 +1193,7 @@
         <v>0.82373791372955951</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>6</v>
       </c>
@@ -1206,7 +1207,7 @@
         <v>-0.70787705055813721</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>7</v>
       </c>
@@ -1225,16 +1226,16 @@
         <v>8</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D56" s="4">
-        <v>0.68907593118401889</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+        <v>0.56594453074999673</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>3</v>
       </c>
@@ -1248,7 +1249,7 @@
         <v>0.80369910334616002</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>5</v>
       </c>
@@ -1262,7 +1263,7 @@
         <v>0.85959541399075923</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>6</v>
       </c>
@@ -1276,7 +1277,7 @@
         <v>-0.63183122360981203</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>7</v>
       </c>
@@ -1298,13 +1299,13 @@
         <v>5</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D61" s="4">
-        <v>0.51641786891722319</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+        <v>0.56404813637263529</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>3</v>
       </c>
@@ -1318,7 +1319,7 @@
         <v>-0.71374883016685164</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>5</v>
       </c>
@@ -1332,7 +1333,7 @@
         <v>-0.6305557582858502</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>6</v>
       </c>
@@ -1346,7 +1347,7 @@
         <v>0.77536888467174403</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>7</v>
       </c>
@@ -1365,16 +1366,16 @@
         <v>8</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D66" s="4">
-        <v>-0.58564535026855558</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+        <v>0.51641786891722319</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>3</v>
       </c>
@@ -1388,7 +1389,7 @@
         <v>0.46251860530097222</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>5</v>
       </c>
@@ -1402,7 +1403,7 @@
         <v>0.65335964168237304</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>6</v>
       </c>
@@ -1416,7 +1417,7 @@
         <v>-0.15386457879305529</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>7</v>
       </c>
@@ -1435,16 +1436,16 @@
         <v>8</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D71" s="4">
-        <v>0.1462666456689265</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+        <v>0.49423181455165471</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>3</v>
       </c>
@@ -1458,7 +1459,7 @@
         <v>0.64575517635531299</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>5</v>
       </c>
@@ -1472,7 +1473,7 @@
         <v>0.43761869077876753</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>6</v>
       </c>
@@ -1486,7 +1487,7 @@
         <v>-0.45382477530962312</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>7</v>
       </c>
@@ -1505,16 +1506,16 @@
         <v>8</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D76" s="4">
-        <v>0.67408690543250938</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+        <v>0.48599620399760468</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
         <v>3</v>
       </c>
@@ -1528,7 +1529,7 @@
         <v>0.95570302255305095</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
         <v>5</v>
       </c>
@@ -1542,7 +1543,7 @@
         <v>0.87434839673961318</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
         <v>6</v>
       </c>
@@ -1556,7 +1557,7 @@
         <v>-0.77616785184864001</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
         <v>7</v>
       </c>
@@ -1575,16 +1576,16 @@
         <v>8</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D81" s="4">
-        <v>0.76257625978730981</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+        <v>0.16646496057656529</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
         <v>3</v>
       </c>
@@ -1598,7 +1599,7 @@
         <v>0.89457967723371534</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>5</v>
       </c>
@@ -1612,7 +1613,7 @@
         <v>0.99270178843834178</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
         <v>6</v>
       </c>
@@ -1626,7 +1627,7 @@
         <v>-0.78829325318893262</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
         <v>7</v>
       </c>
@@ -1645,16 +1646,16 @@
         <v>8</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D86" s="4">
-        <v>0.56404813637263529</v>
-      </c>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+        <v>0.1462666456689265</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
         <v>3</v>
       </c>
@@ -1668,7 +1669,7 @@
         <v>-0.78371468880580952</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
         <v>5</v>
       </c>
@@ -1682,7 +1683,7 @@
         <v>-0.77144419023946065</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
         <v>6</v>
       </c>
@@ -1696,7 +1697,7 @@
         <v>0.98248567227391159</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
         <v>7</v>
       </c>
@@ -1715,16 +1716,16 @@
         <v>8</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D91" s="4">
-        <v>-0.59885733516535478</v>
-      </c>
-    </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+        <v>0.1205513538615286</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
         <v>3</v>
       </c>
@@ -1738,7 +1739,7 @@
         <v>0.48852111649936769</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>5</v>
       </c>
@@ -1752,7 +1753,7 @@
         <v>0.6804016337770058</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
         <v>6</v>
       </c>
@@ -1766,7 +1767,7 @@
         <v>-0.11542822820072721</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
         <v>7</v>
       </c>
@@ -1788,13 +1789,13 @@
         <v>7</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D96" s="4">
-        <v>0.16646496057656529</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+        <v>4.3551084891451229E-2</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
         <v>3</v>
       </c>
@@ -1808,7 +1809,7 @@
         <v>0.78683362544686941</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
         <v>5</v>
       </c>
@@ -1822,7 +1823,7 @@
         <v>0.57311779313517763</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
         <v>6</v>
       </c>
@@ -1836,7 +1837,7 @@
         <v>-0.59844748749700127</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
         <v>7</v>
       </c>
@@ -1855,16 +1856,16 @@
         <v>8</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D101" s="4">
-        <v>0.82268063781526812</v>
-      </c>
-    </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+        <v>1.6820872551199791E-2</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
         <v>3</v>
       </c>
@@ -1878,7 +1879,7 @@
         <v>0.90759659946555304</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
         <v>5</v>
       </c>
@@ -1892,7 +1893,7 @@
         <v>0.93334174014954552</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
         <v>6</v>
       </c>
@@ -1906,7 +1907,7 @@
         <v>-0.76489240669286696</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
         <v>7</v>
       </c>
@@ -1925,16 +1926,16 @@
         <v>8</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D106" s="4">
-        <v>0.63771350176580899</v>
-      </c>
-    </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+        <v>-0.56526137107275565</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
         <v>3</v>
       </c>
@@ -1948,7 +1949,7 @@
         <v>0.8459676441589169</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
         <v>5</v>
       </c>
@@ -1962,7 +1963,7 @@
         <v>0.98951809344835107</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
         <v>6</v>
       </c>
@@ -1976,7 +1977,7 @@
         <v>-0.75967468702902707</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
         <v>7</v>
       </c>
@@ -1995,16 +1996,16 @@
         <v>8</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D111" s="4">
-        <v>0.49423181455165471</v>
-      </c>
-    </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+        <v>-0.58564535026855558</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
         <v>3</v>
       </c>
@@ -2018,7 +2019,7 @@
         <v>-0.77682802182905109</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
         <v>5</v>
       </c>
@@ -2032,7 +2033,7 @@
         <v>-0.77031074030932545</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
         <v>6</v>
       </c>
@@ -2046,7 +2047,7 @@
         <v>0.98675748669042562</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
         <v>7</v>
       </c>
@@ -2074,7 +2075,7 @@
         <v>-0.59192944260877245</v>
       </c>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
         <v>3</v>
       </c>
@@ -2088,7 +2089,7 @@
         <v>0.3290117430710201</v>
       </c>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
         <v>5</v>
       </c>
@@ -2102,7 +2103,7 @@
         <v>0.56289946570777971</v>
       </c>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
         <v>6</v>
       </c>
@@ -2116,7 +2117,7 @@
         <v>2.6172249503399941E-2</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
         <v>7</v>
       </c>
@@ -2135,16 +2136,16 @@
         <v>8</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D121" s="4">
-        <v>1.6820872551199791E-2</v>
-      </c>
-    </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
+        <v>-0.59885733516535478</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
         <v>3</v>
       </c>
@@ -2158,7 +2159,7 @@
         <v>0.60251232837022217</v>
       </c>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
         <v>5</v>
       </c>
@@ -2172,7 +2173,7 @@
         <v>0.440462298722682</v>
       </c>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
         <v>6</v>
       </c>
@@ -2186,7 +2187,7 @@
         <v>-0.44928446834063052</v>
       </c>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
         <v>7</v>
       </c>
@@ -2205,17 +2206,26 @@
         <v>8</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D126" s="4">
-        <v>0.63635854003269621</v>
+        <v>-0.6181901436689502</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:D126" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="Licht_lux"/>
+      </filters>
+    </filterColumn>
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A6:D126">
+      <sortCondition descending="1" ref="D1:D126"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>